--- a/website-sync/public/downloads/ResourceLoadSampleData.xlsx
+++ b/website-sync/public/downloads/ResourceLoadSampleData.xlsx
@@ -7,19 +7,23 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Assignments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tasks" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tasks'!$A$1:$G$13</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,16 +31,37 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000F3D36"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A6B5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3FAF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,13 +69,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9D2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9D2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9D2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9D2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,357 +465,429 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Progress</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>End Date</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Progress</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RAG</t>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Project</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Ada Ng</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Website redesign</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>North Sea Hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>API design</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>46204</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="C3" s="6" t="n">
+        <v>46223</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Sam Ortiz</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>North Sea Hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>FAT prep</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ada Ng</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>North Sea Hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Cable pull</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Bo Berg</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Arctic Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Weather hold</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Riley Chen</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Arctic Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>On-call week</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Bo Berg</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Arctic Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Scope workshop</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>46214</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>46228</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Initiation</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Cara Diaz</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Yard Retrofit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Scope freeze</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Initiation</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Cara Diaz</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Yard Retrofit</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Sam Ortiz</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Digital Twin v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Ada Ng</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Digital Twin v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Permit draft</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>46249</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ada Ng</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Brand guidelines</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46264</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bjørn Holm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Data platform</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bjørn Holm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>API hardening</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46259</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Bjørn Holm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>On-call week</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cara Moss</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Customer onboard</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cara Moss</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Q3 planning</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
+      <c r="C12" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Finn Olsen</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Port Expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Stakeholder map</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
         <v>46254</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>46270</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>PMO</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Diego Ruiz</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mobile app v2</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>46208</v>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="C13" s="6" t="n">
         <v>46280</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Elena Park</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Security audit</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Elena Park</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Vendor RFP</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Procurement</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Green</t>
+      <c r="D13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Jordan Lee</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Port Expansion</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>